--- a/data/trans_dic/P6907S1-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6907S1-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene algún otro problema</t>
+          <t>Población que su trabajo le afecta de manera que tiene algún otro problema (tasa de respuesta: 88,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,61</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,08</t>
+          <t>0,0; 25,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,63</t>
+          <t>0,0; 27,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,51</t>
+          <t>0,0; 57,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,68</t>
+          <t>0,0; 10,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,91</t>
+          <t>0,0; 18,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,04</t>
+          <t>0,0; 50,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 22,76</t>
+          <t>9,8; 23,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 16,93</t>
+          <t>2,11; 18,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 12,28</t>
+          <t>1,24; 12,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 28,3</t>
+          <t>0,6; 30,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 22,81</t>
+          <t>7,71; 24,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,61</t>
+          <t>0,0; 13,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,24</t>
+          <t>0,0; 17,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 24,77</t>
+          <t>3,99; 24,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,62; 21,21</t>
+          <t>10,41; 21,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 12,25</t>
+          <t>1,36; 13,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,12</t>
+          <t>2,16; 10,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 19,27</t>
+          <t>4,07; 20,2</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,31</t>
+          <t>3,56; 12,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 19,78</t>
+          <t>2,33; 21,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,78</t>
+          <t>0,82; 8,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 23,42</t>
+          <t>8,12; 23,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 17,68</t>
+          <t>3,79; 18,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,17</t>
+          <t>0,0; 14,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,86</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 15,64</t>
+          <t>4,25; 15,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 11,83</t>
+          <t>4,39; 12,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 13,85</t>
+          <t>2,32; 13,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,71</t>
+          <t>0,95; 5,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,83; 17,53</t>
+          <t>8,28; 17,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 14,58</t>
+          <t>3,42; 13,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,69</t>
+          <t>1,18; 9,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 15,44</t>
+          <t>3,83; 14,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 25,17</t>
+          <t>2,74; 26,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,47</t>
+          <t>0,0; 9,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,9</t>
+          <t>2,18; 9,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 14,7</t>
+          <t>4,82; 14,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,44</t>
+          <t>0,75; 7,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 10,48</t>
+          <t>3,78; 10,51</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 18,17</t>
+          <t>2,08; 19,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,74</t>
+          <t>0,0; 21,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 21,77</t>
+          <t>7,03; 23,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,92</t>
+          <t>0,0; 35,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,78</t>
+          <t>0,0; 17,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 17,97</t>
+          <t>5,0; 17,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 17,63</t>
+          <t>3,17; 17,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,19</t>
+          <t>0,0; 16,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,57; 18,07</t>
+          <t>7,41; 17,43</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,13</t>
+          <t>6,84; 12,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 9,72</t>
+          <t>2,6; 10,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,03</t>
+          <t>1,76; 5,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,88; 15,11</t>
+          <t>7,76; 15,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,33; 15,58</t>
+          <t>7,24; 16,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,73</t>
+          <t>0,86; 7,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,44</t>
+          <t>0,88; 5,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,59</t>
+          <t>5,48; 11,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,22</t>
+          <t>7,53; 12,22</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,57</t>
+          <t>2,25; 7,74</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,76</t>
+          <t>1,85; 5,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,05</t>
+          <t>7,24; 12,19</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene algún otro problema</t>
+          <t>Población que su trabajo le afecta de manera que tiene algún otro problema (tasa de respuesta: 88,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4437</t>
+          <t>0; 3608</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 954</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5159</t>
+          <t>0; 4333</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2171</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5488</t>
+          <t>0; 5415</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1330</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1689</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9745</t>
+          <t>0; 8806</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6393</t>
+          <t>0; 7112</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1534</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6883</t>
+          <t>0; 5360</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 11102</t>
+          <t>0; 10846</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12993; 32386</t>
+          <t>13940; 33848</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>831; 6536</t>
+          <t>816; 6986</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1013; 10020</t>
+          <t>1010; 10187</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>482; 16719</t>
+          <t>354; 18273</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5955; 18082</t>
+          <t>6116; 19054</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4961</t>
+          <t>0; 4005</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7979</t>
+          <t>0; 8297</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2096; 12372</t>
+          <t>1992; 12470</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23523; 46993</t>
+          <t>23071; 46765</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>945; 8389</t>
+          <t>931; 9114</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2685; 12944</t>
+          <t>2759; 13192</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4663; 21005</t>
+          <t>4434; 22027</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4494; 15513</t>
+          <t>4489; 15365</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1052; 8659</t>
+          <t>1019; 9259</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>942; 8804</t>
+          <t>930; 9506</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7392; 22369</t>
+          <t>7759; 22515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2245; 12385</t>
+          <t>2655; 12656</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6120</t>
+          <t>0; 6389</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>0; 4391</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3434; 11815</t>
+          <t>3213; 11937</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8345; 23188</t>
+          <t>8598; 23875</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2034; 12039</t>
+          <t>2021; 11701</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1745; 10541</t>
+          <t>1759; 9558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13404; 29989</t>
+          <t>14172; 29505</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3917; 16196</t>
+          <t>3796; 15511</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1974</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1083; 8855</t>
+          <t>1076; 8970</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3593; 16764</t>
+          <t>4163; 15979</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1078; 9320</t>
+          <t>1016; 9715</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1859</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5316</t>
+          <t>0; 5345</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3465; 13793</t>
+          <t>3376; 14045</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7157; 21773</t>
+          <t>7137; 22029</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 1990</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1120; 10972</t>
+          <t>1106; 11009</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9746; 27628</t>
+          <t>9971; 27695</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>946; 8338</t>
+          <t>953; 9069</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4708</t>
+          <t>0; 4473</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2090</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4818; 14680</t>
+          <t>4742; 15634</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4996</t>
+          <t>0; 4943</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1764</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5475</t>
+          <t>0; 5314</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2595; 9972</t>
+          <t>2777; 9689</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1859; 10539</t>
+          <t>1894; 10758</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 4093</t>
+          <t>0; 5079</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5618</t>
+          <t>0; 5568</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9305; 22215</t>
+          <t>9110; 21430</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 894</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 916</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 633</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 633</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31374; 57283</t>
+          <t>32292; 57892</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3828; 13864</t>
+          <t>3708; 15108</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6822; 21090</t>
+          <t>6155; 20359</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26759; 51294</t>
+          <t>26360; 51777</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>16145; 34298</t>
+          <t>15931; 35361</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>901; 7739</t>
+          <t>865; 7292</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1873; 11770</t>
+          <t>1914; 12838</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>19193; 41055</t>
+          <t>19415; 41707</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>52223; 84638</t>
+          <t>52127; 84594</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5690; 18377</t>
+          <t>5467; 18786</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10744; 26956</t>
+          <t>10465; 29009</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>49477; 83611</t>
+          <t>50220; 84552</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6907S1-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6907S1-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 9,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,26</t>
+          <t>0,0; 24,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,27</t>
+          <t>0,0; 22,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,39</t>
+          <t>0,0; 56,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,77</t>
+          <t>0,0; 9,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,61</t>
+          <t>0,0; 14,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,84</t>
+          <t>0,0; 44,65</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,8; 23,79</t>
+          <t>9,51; 22,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 18,09</t>
+          <t>2,16; 19,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 12,49</t>
+          <t>1,5; 12,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 30,93</t>
+          <t>1,82; 26,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 24,03</t>
+          <t>6,82; 22,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,41</t>
+          <t>0,0; 18,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,92</t>
+          <t>0,0; 19,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 24,96</t>
+          <t>4,18; 24,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,41; 21,11</t>
+          <t>10,5; 20,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 13,31</t>
+          <t>1,38; 12,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,32</t>
+          <t>2,22; 10,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 20,2</t>
+          <t>5,19; 22,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 12,19</t>
+          <t>3,49; 12,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 21,15</t>
+          <t>2,36; 21,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,4</t>
+          <t>0,81; 8,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 23,57</t>
+          <t>7,25; 20,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 18,07</t>
+          <t>3,9; 17,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,8</t>
+          <t>0,0; 13,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 15,8</t>
+          <t>4,75; 15,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 12,18</t>
+          <t>4,3; 11,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 13,46</t>
+          <t>2,37; 13,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,18</t>
+          <t>0,95; 5,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,28; 17,25</t>
+          <t>7,15; 15,46</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 13,96</t>
+          <t>3,47; 14,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,81</t>
+          <t>1,14; 10,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 14,72</t>
+          <t>3,48; 14,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 26,23</t>
+          <t>4,07; 25,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,17 +1167,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,53</t>
+          <t>0,0; 9,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,06</t>
+          <t>4,52; 11,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 14,87</t>
+          <t>4,73; 14,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,46</t>
+          <t>0,76; 7,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 10,51</t>
+          <t>4,86; 11,18</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 19,77</t>
+          <t>2,0; 18,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,6</t>
+          <t>0,0; 29,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 23,18</t>
+          <t>6,72; 21,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,54</t>
+          <t>0,0; 35,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,25</t>
+          <t>0,0; 18,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 17,46</t>
+          <t>5,44; 17,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 17,99</t>
+          <t>1,66; 16,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,36</t>
+          <t>0,0; 19,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,36</t>
+          <t>0,0; 7,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 17,43</t>
+          <t>7,66; 16,75</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,26</t>
+          <t>6,61; 12,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,6</t>
+          <t>2,62; 10,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,82</t>
+          <t>1,74; 5,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,76; 15,25</t>
+          <t>7,27; 14,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,24; 16,06</t>
+          <t>7,03; 15,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,28</t>
+          <t>0,88; 7,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,94</t>
+          <t>0,81; 5,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,77</t>
+          <t>6,68; 12,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,22</t>
+          <t>7,72; 12,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,74</t>
+          <t>2,42; 7,88</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,12</t>
+          <t>1,91; 4,95</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,24; 12,19</t>
+          <t>7,54; 12,29</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2372</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3608</t>
+          <t>0; 4434</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4333</t>
+          <t>0; 4267</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5415</t>
+          <t>0; 4402</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 8806</t>
+          <t>0; 8907</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 7112</t>
+          <t>0; 6039</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5360</t>
+          <t>0; 4099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 10846</t>
+          <t>0; 11215</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>13097</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13940; 33848</t>
+          <t>13533; 32483</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>816; 6986</t>
+          <t>833; 7363</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1010; 10187</t>
+          <t>1221; 10391</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>354; 18273</t>
+          <t>1266; 18328</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6116; 19054</t>
+          <t>5408; 18066</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4005</t>
+          <t>0; 5577</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 8297</t>
+          <t>0; 8865</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1992; 12470</t>
+          <t>2152; 12796</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23071; 46765</t>
+          <t>23262; 45683</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>931; 9114</t>
+          <t>948; 8776</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2759; 13192</t>
+          <t>2835; 13326</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4434; 22027</t>
+          <t>6283; 27578</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20739</t>
+          <t>21714</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4489; 15365</t>
+          <t>4395; 15483</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1019; 9259</t>
+          <t>1033; 9369</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>930; 9506</t>
+          <t>918; 9102</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7759; 22515</t>
+          <t>7971; 21996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2655; 12656</t>
+          <t>2729; 12072</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6389</t>
+          <t>0; 5839</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4391</t>
+          <t>0; 4078</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3213; 11937</t>
+          <t>4114; 13170</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8598; 23875</t>
+          <t>8428; 22579</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2021; 11701</t>
+          <t>2059; 11858</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1759; 9558</t>
+          <t>1745; 9613</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14172; 29505</t>
+          <t>14050; 30407</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>18618</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3796; 15511</t>
+          <t>3857; 15913</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1076; 8970</t>
+          <t>1043; 9223</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4163; 15979</t>
+          <t>4198; 18019</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1016; 9715</t>
+          <t>1507; 9559</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2722,17 +2722,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5345</t>
+          <t>0; 5396</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3376; 14045</t>
+          <t>5725; 15108</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7137; 22029</t>
+          <t>7006; 22061</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1106; 11009</t>
+          <t>1129; 10821</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9971; 27695</t>
+          <t>12004; 27631</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14690</t>
+          <t>15551</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>953; 9069</t>
+          <t>917; 8405</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4473</t>
+          <t>0; 6036</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4742; 15634</t>
+          <t>4839; 15330</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4943</t>
+          <t>0; 4960</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2930,32 +2930,32 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5314</t>
+          <t>0; 5603</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2777; 9689</t>
+          <t>3360; 10891</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1894; 10758</t>
+          <t>993; 9834</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5079</t>
+          <t>0; 6113</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5568</t>
+          <t>0; 5628</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9110; 21430</t>
+          <t>10242; 22413</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>39513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>65613</t>
+          <t>71351</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>32292; 57892</t>
+          <t>31212; 58423</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3708; 15108</t>
+          <t>3736; 14741</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6155; 20359</t>
+          <t>6088; 20082</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26360; 51777</t>
+          <t>27991; 56998</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15931; 35361</t>
+          <t>15468; 33934</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>865; 7292</t>
+          <t>881; 7526</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1914; 12838</t>
+          <t>1754; 11305</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>19415; 41707</t>
+          <t>23061; 43184</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>52127; 84594</t>
+          <t>53477; 84837</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5467; 18786</t>
+          <t>5871; 19125</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10465; 29009</t>
+          <t>10833; 28057</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>50220; 84552</t>
+          <t>55032; 89745</t>
         </is>
       </c>
     </row>
